--- a/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_Master_Information_Delivery_Plan.xlsx
@@ -5013,7 +5013,7 @@
       <c r="C58" s="12" t="inlineStr"/>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Asset data capture: serial numbers and installation dates</t>
+          <t>Asset data capture (tiered schedule, BEP section 14)</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -5070,7 +5070,7 @@
       <c r="Q58" s="14" t="inlineStr"/>
       <c r="R58" s="13" t="inlineStr">
         <is>
-          <t>Required for LOD 500; reported monthly from the first month of construction</t>
+          <t>Tier A serialised plant, Tier B maintainable devices, Tier C warranted fabric. Required for LOD 500; reported monthly from the first month of construction</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       <c r="Q59" s="14" t="inlineStr"/>
       <c r="R59" s="13" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Monthly, by tier and by volume. A tier below 95 per cent at the Deliverable D gate is a gate failure</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       <c r="Q64" s="14" t="inlineStr"/>
       <c r="R64" s="13" t="inlineStr">
         <is>
-          <t>Includes asset data</t>
+          <t>Includes Tier A and Tier B asset data</t>
         </is>
       </c>
     </row>

--- a/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_Master_Information_Delivery_Plan.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MIDP'!$A$1:$R$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MIDP'!$A$1:$R$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'MIDP'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>KUT-PLN-ZZ-ZZ-SC-Z-0001</t>
+          <t>KUT-SMB-ZZ-ZZ-SC-Z-0001</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Planscape Consulting Engineers Ltd (Information Manager)</t>
+          <t>Symbion Consulting Group Studios (Information Manager)</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1348,18 +1348,18 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Z-006</t>
+          <t>Z-007</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>All disciplines</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr"/>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Task Information Delivery Plan</t>
+          <t>Standards reconciliation schedule (BEP section 4.1.3)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>DOCX/PDF</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1405,25 +1405,25 @@
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>Task Team Managers</t>
+          <t>All disciplines</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>TIDP-ALL</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q8" s="14" t="inlineStr"/>
       <c r="R8" s="13" t="inlineStr">
         <is>
-          <t>One per appointed party</t>
+          <t>Opened at mobilisation; CLOSED before Technical Design. An open row means two parties may design to different bases</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Z-010</t>
+          <t>Z-008</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1434,7 +1434,7 @@
       <c r="C9" s="12" t="inlineStr"/>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Federated coordination model</t>
+          <t>Shared coordinates seed model</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1444,32 +1444,32 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>NWC/IFC</t>
+          <t>RVT</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L9" s="15" t="n"/>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>BIM Coordinator</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
@@ -1491,60 +1491,60 @@
       <c r="Q9" s="14" t="inlineStr"/>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>First federation</t>
+          <t>Survey point, project base point, true north, levels and grids. Every model acquires coordinates from it</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>A-100</t>
+          <t>Z-009</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Architectural model</t>
+          <t>Level and grid register</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>XLSX/PDF</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L10" s="15" t="n"/>
@@ -1555,71 +1555,71 @@
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q10" s="14" t="inlineStr"/>
       <c r="R10" s="13" t="inlineStr">
         <is>
-          <t>Massing and generic systems; rooms placed</t>
+          <t>Level codes appear in every container name</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>S-100</t>
+          <t>Z-011</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Structural model</t>
+          <t>Software and version register</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
@@ -1630,71 +1630,71 @@
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>All parties</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q11" s="14" t="inlineStr"/>
       <c r="R11" s="13" t="inlineStr">
         <is>
-          <t>Indicative frame and foundations</t>
+          <t>One authoring version project-wide for the duration of a stage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>M-100</t>
+          <t>Z-012</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Mechanical model</t>
+          <t>CDE folder structure and permission matrix</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L12" s="15" t="n"/>
@@ -1705,71 +1705,67 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q12" s="14" t="inlineStr"/>
-      <c r="R12" s="13" t="inlineStr">
-        <is>
-          <t>Plant space allocation, primary routes</t>
-        </is>
-      </c>
+      <c r="R12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>E-100</t>
+          <t>Z-013</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr"/>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Electrical model</t>
+          <t>Information classification and access schedule</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L13" s="15" t="n"/>
@@ -1780,61 +1776,61 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Appointing Party</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>TIDP-E</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q13" s="14" t="inlineStr"/>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Plant space allocation, primary routes</t>
+          <t>Restricted spaces and systems must be classified BEFORE modelling begins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>P-100</t>
+          <t>Z-014</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr"/>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Plumbing and drainage model</t>
+          <t>Clash matrix and tolerance schedule</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
@@ -1855,71 +1851,71 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>MEP and structural leads</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>TIDP-P</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q14" s="14" t="inlineStr"/>
       <c r="R14" s="13" t="inlineStr">
         <is>
-          <t>Primary routes</t>
+          <t>Required before the first coordination cycle of Stage 2.2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>G-100</t>
+          <t>Z-015</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Civil and Site</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr"/>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Site model and levels</t>
+          <t>IFC export configuration</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF/JSON</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L15" s="15" t="n"/>
@@ -1930,25 +1926,25 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Civil lead</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr"/>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Site levels, access, drainage strategy</t>
+          <t>Issued centrally, or every consultant IFC differs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Z-110</t>
+          <t>Z-016</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -1959,7 +1955,7 @@
       <c r="C16" s="12" t="inlineStr"/>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Basis of design report</t>
+          <t>Shared parameter file</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1969,32 +1965,32 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>DOCX/PDF</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L16" s="15" t="n"/>
@@ -2005,7 +2001,7 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>Lead Appointed Party</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
@@ -2016,14 +2012,14 @@
       <c r="Q16" s="14" t="inlineStr"/>
       <c r="R16" s="13" t="inlineStr">
         <is>
-          <t>Design intent</t>
+          <t>Central ownership; a locally added parameter has a different GUID</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Z-111</t>
+          <t>Z-017</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -2034,27 +2030,27 @@
       <c r="C17" s="12" t="inlineStr"/>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Area schedule reconciled to the brief</t>
+          <t>Capability and capacity assessment</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>XLSX/PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -2080,7 +2076,7 @@
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -2091,25 +2087,25 @@
       <c r="Q17" s="14" t="inlineStr"/>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>Gate condition</t>
+          <t>ISO 19650-2; the Stage 0 test model is its practical form</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Z-112</t>
+          <t>Z-006</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>All disciplines</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr"/>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Deliverable A gate pack</t>
+          <t>Task Information Delivery Plan</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -2119,22 +2115,22 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>2.1 Deliverable A</t>
+          <t>Mobilisation</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -2144,7 +2140,7 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="L18" s="15" t="n"/>
@@ -2155,36 +2151,36 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Task Team Managers</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-ALL</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr"/>
       <c r="R18" s="13" t="inlineStr">
         <is>
-          <t>Contents per the playbook, Appendix B</t>
+          <t>One per appointed party</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>A-200</t>
+          <t>Z-010</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr"/>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Architectural model</t>
+          <t>Federated coordination model</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -2194,22 +2190,22 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>NWC/IFC</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -2219,7 +2215,7 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L19" s="15" t="n"/>
@@ -2230,25 +2226,25 @@
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>BIM Coordinator</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr"/>
       <c r="R19" s="13" t="inlineStr">
         <is>
-          <t>Real geometry, correctly located</t>
+          <t>First federation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-100</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -2259,27 +2255,27 @@
       <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>General arrangement plans, sections and elevations (50%)</t>
+          <t>Architectural model</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -2294,7 +2290,7 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L20" s="15" t="n"/>
@@ -2314,43 +2310,47 @@
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr"/>
-      <c r="R20" s="13" t="inlineStr"/>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>Massing and generic systems; rooms placed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>S-100</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Door and window schedules</t>
+          <t>Structural model</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>PDF/XLSX</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L21" s="15" t="n"/>
@@ -2376,52 +2376,56 @@
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>Structural lead</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-S</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr"/>
-      <c r="R21" s="13" t="inlineStr"/>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>Indicative frame and foundations</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>A-203</t>
+          <t>M-100</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Room data sheets (key spaces)</t>
+          <t>Mechanical model</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Room data sheet</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L22" s="15" t="n"/>
@@ -2447,52 +2451,56 @@
       </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-M</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr"/>
-      <c r="R22" s="13" t="inlineStr"/>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>Plant space allocation, primary routes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>A-204</t>
+          <t>E-100</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr"/>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Existing conditions and removals plan</t>
+          <t>Electrical model</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -2507,7 +2515,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L23" s="15" t="n"/>
@@ -2518,36 +2526,36 @@
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-E</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr"/>
       <c r="R23" s="13" t="inlineStr">
         <is>
-          <t>Demolition classification is a manual task; see BEP 10.3</t>
+          <t>Plant space allocation, primary routes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>S-200</t>
+          <t>P-100</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr"/>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Structural model</t>
+          <t>Plumbing and drainage model</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -2557,12 +2565,12 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -2582,7 +2590,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L24" s="15" t="n"/>
@@ -2593,56 +2601,56 @@
       </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-P</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr"/>
       <c r="R24" s="13" t="inlineStr">
         <is>
-          <t>Sized members; penetrations coordinated</t>
+          <t>Primary routes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>S-201</t>
+          <t>G-100</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Civil and Site</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>General arrangement drawings (50%)</t>
+          <t>Site model and levels</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -2657,7 +2665,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L25" s="15" t="n"/>
@@ -2668,57 +2676,61 @@
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>Civil lead</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-G</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr"/>
-      <c r="R25" s="13" t="inlineStr"/>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>Site levels, access, drainage strategy</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>M-200</t>
+          <t>Z-110</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Mechanical model</t>
+          <t>Basis of design report</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>DOCX/PDF</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
@@ -2728,7 +2740,7 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L26" s="15" t="n"/>
@@ -2739,61 +2751,61 @@
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr"/>
       <c r="R26" s="13" t="inlineStr">
         <is>
-          <t>Real equipment; risers fixed</t>
+          <t>Design intent</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>M-201</t>
+          <t>Z-111</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr"/>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>HVAC layouts (50%)</t>
+          <t>Area schedule reconciled to the brief</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>XLSX/PDF</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
@@ -2803,7 +2815,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L27" s="15" t="n"/>
@@ -2814,57 +2826,61 @@
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr"/>
-      <c r="R27" s="13" t="inlineStr"/>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>Gate condition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>E-200</t>
+          <t>Z-112</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Electrical model</t>
+          <t>Deliverable A gate pack</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.1 Deliverable A</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
@@ -2874,7 +2890,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="L28" s="15" t="n"/>
@@ -2885,37 +2901,41 @@
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>TIDP-E</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr"/>
-      <c r="R28" s="13" t="inlineStr"/>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t>Contents per the playbook, Appendix B</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>E-201</t>
+          <t>A-200</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr"/>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Power and lighting layouts (50%)</t>
+          <t>Architectural model</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -2930,7 +2950,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -2956,37 +2976,41 @@
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>TIDP-E</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr"/>
-      <c r="R29" s="13" t="inlineStr"/>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>Real geometry, correctly located</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>P-200</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr"/>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Plumbing and drainage model</t>
+          <t>General arrangement plans, sections and elevations (50%)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -3001,7 +3025,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -3027,12 +3051,12 @@
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>TIDP-P</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr"/>
@@ -3041,23 +3065,23 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>FP-200</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr"/>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>Fire strategy and suppression layout</t>
+          <t>Door and window schedules</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -3072,7 +3096,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>PDF/XLSX</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -3098,12 +3122,12 @@
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q31" s="14" t="inlineStr"/>
@@ -3112,23 +3136,23 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Z-210</t>
+          <t>A-203</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Coordination report</t>
+          <t>Room data sheets (key spaces)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Room data sheet</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -3143,7 +3167,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>PDF/BCF</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -3169,41 +3193,37 @@
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>BIM Coordinator</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q32" s="14" t="inlineStr"/>
-      <c r="R32" s="13" t="inlineStr">
-        <is>
-          <t>No unresolved high priority clashes</t>
-        </is>
-      </c>
+      <c r="R32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Z-211</t>
+          <t>A-204</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Federated model</t>
+          <t>Existing conditions and removals plan</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3218,7 +3238,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>NWC/IFC</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -3244,37 +3264,41 @@
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>BIM Coordinator</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr"/>
-      <c r="R33" s="13" t="inlineStr"/>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>Demolition classification is a manual task; see BEP 10.4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Z-212</t>
+          <t>S-200</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>QS / Cost</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Bill of quantities (preliminary)</t>
+          <t>Structural model</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -3289,7 +3313,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
@@ -3315,37 +3339,41 @@
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>Quantity Surveyor</t>
+          <t>Structural lead</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Q</t>
+          <t>TIDP-S</t>
         </is>
       </c>
       <c r="Q34" s="14" t="inlineStr"/>
-      <c r="R34" s="13" t="inlineStr"/>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t>Sized members; penetrations coordinated</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>FF-200</t>
+          <t>S-201</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>FF&amp;E</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>FF&amp;E and finishes register (first exchange)</t>
+          <t>General arrangement drawings (50%)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -3360,7 +3388,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>CSV/XLSX</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -3386,41 +3414,37 @@
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Interior Designer</t>
+          <t>Structural lead</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-S</t>
         </is>
       </c>
       <c r="Q35" s="14" t="inlineStr"/>
-      <c r="R35" s="13" t="inlineStr">
-        <is>
-          <t>Matched on room number</t>
-        </is>
-      </c>
+      <c r="R35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Z-213</t>
+          <t>M-200</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr"/>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Deliverable B gate pack</t>
+          <t>Mechanical model</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -3435,12 +3459,12 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -3461,57 +3485,61 @@
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-M</t>
         </is>
       </c>
       <c r="Q36" s="14" t="inlineStr"/>
-      <c r="R36" s="13" t="inlineStr"/>
+      <c r="R36" s="13" t="inlineStr">
+        <is>
+          <t>Real equipment; risers fixed</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>A-300</t>
+          <t>M-201</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr"/>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Architectural model</t>
+          <t>HVAC layouts (50%)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
@@ -3521,7 +3549,7 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L37" s="15" t="n"/>
@@ -3532,61 +3560,57 @@
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-M</t>
         </is>
       </c>
       <c r="Q37" s="14" t="inlineStr"/>
-      <c r="R37" s="13" t="inlineStr">
-        <is>
-          <t>Interfaces resolved</t>
-        </is>
-      </c>
+      <c r="R37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>A-301</t>
+          <t>E-200</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Full drawing set (100%) and details</t>
+          <t>Electrical model</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
@@ -3596,7 +3620,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L38" s="15" t="n"/>
@@ -3607,12 +3631,12 @@
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-E</t>
         </is>
       </c>
       <c r="Q38" s="14" t="inlineStr"/>
@@ -3621,43 +3645,43 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>S-300</t>
+          <t>E-201</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Structural model</t>
+          <t>Power and lighting layouts (50%)</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -3667,7 +3691,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L39" s="15" t="n"/>
@@ -3678,61 +3702,57 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-E</t>
         </is>
       </c>
       <c r="Q39" s="14" t="inlineStr"/>
-      <c r="R39" s="13" t="inlineStr">
-        <is>
-          <t>Connections resolved</t>
-        </is>
-      </c>
+      <c r="R39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>S-301</t>
+          <t>P-200</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Structural drawing set (100%)</t>
+          <t>Plumbing and drainage model</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
@@ -3742,7 +3762,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L40" s="15" t="n"/>
@@ -3753,12 +3773,12 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-P</t>
         </is>
       </c>
       <c r="Q40" s="14" t="inlineStr"/>
@@ -3767,33 +3787,33 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>M-300</t>
+          <t>FP-200</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr"/>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Mechanical model and drawing set (100%)</t>
+          <t>Fire strategy and suppression layout</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -3803,7 +3823,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -3813,7 +3833,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L41" s="15" t="n"/>
@@ -3824,61 +3844,57 @@
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-FP</t>
         </is>
       </c>
       <c r="Q41" s="14" t="inlineStr"/>
-      <c r="R41" s="13" t="inlineStr">
-        <is>
-          <t>BMS points identified</t>
-        </is>
-      </c>
+      <c r="R41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>E-300</t>
+          <t>Z-210</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr"/>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Electrical model and drawing set (100%)</t>
+          <t>Coordination report</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>PDF/BCF</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
@@ -3888,7 +3904,7 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L42" s="15" t="n"/>
@@ -3899,57 +3915,61 @@
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>BIM Coordinator</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>TIDP-E</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q42" s="14" t="inlineStr"/>
-      <c r="R42" s="13" t="inlineStr"/>
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>No unresolved high priority clashes</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>P-300</t>
+          <t>Z-211</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr"/>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Plumbing model and drawing set (100%)</t>
+          <t>Federated model</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>NWC/IFC</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
@@ -3959,7 +3979,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L43" s="15" t="n"/>
@@ -3970,12 +3990,12 @@
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>BIM Coordinator</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>TIDP-P</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q43" s="14" t="inlineStr"/>
@@ -3984,43 +4004,43 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>FP-300</t>
+          <t>Z-212</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>QS / Cost</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Fire strategy and model (100%)</t>
+          <t>Bill of quantities (preliminary)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
@@ -4030,7 +4050,7 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L44" s="15" t="n"/>
@@ -4041,12 +4061,12 @@
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>Quantity Surveyor</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Q</t>
         </is>
       </c>
       <c r="Q44" s="14" t="inlineStr"/>
@@ -4055,43 +4075,43 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>LV-300</t>
+          <t>FF-200</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Low Voltage</t>
+          <t>FF&amp;E</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Communications and security model</t>
+          <t>FF&amp;E and finishes register (first exchange)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>CSV/XLSX</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
@@ -4101,7 +4121,7 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L45" s="15" t="n"/>
@@ -4112,52 +4132,56 @@
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>LV lead</t>
+          <t>Interior Designer</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-FF</t>
         </is>
       </c>
       <c r="Q45" s="14" t="inlineStr"/>
-      <c r="R45" s="13" t="inlineStr"/>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>Matched on room number</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Z-310</t>
+          <t>Z-213</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>QS / Cost</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Bill of quantities (tender)</t>
+          <t>Deliverable B gate pack</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -4172,7 +4196,7 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="L46" s="15" t="n"/>
@@ -4183,12 +4207,12 @@
       </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
-          <t>Quantity Surveyor</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Q</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q46" s="14" t="inlineStr"/>
@@ -4197,23 +4221,23 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Z-311</t>
+          <t>A-300</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr"/>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Specifications</t>
+          <t>Architectural model</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Specification</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -4228,7 +4252,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -4254,37 +4278,41 @@
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Lead Appointed Party</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q47" s="14" t="inlineStr"/>
-      <c r="R47" s="13" t="inlineStr"/>
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>Interfaces resolved</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Z-312</t>
+          <t>A-301</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Specification reconciliation report</t>
+          <t>Full drawing set (100%) and details</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -4299,7 +4327,7 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>XLSX/PDF</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
@@ -4325,41 +4353,37 @@
       </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Architecture lead</t>
         </is>
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-A</t>
         </is>
       </c>
       <c r="Q48" s="14" t="inlineStr"/>
-      <c r="R48" s="13" t="inlineStr">
-        <is>
-          <t>Gaps closed or formally accepted</t>
-        </is>
-      </c>
+      <c r="R48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>FF-300</t>
+          <t>S-300</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>FF&amp;E</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr"/>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>FF&amp;E specifications and schedule</t>
+          <t>Structural model</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4374,7 +4398,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>XLSX/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -4400,37 +4424,41 @@
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Interior Designer</t>
+          <t>Structural lead</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-S</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr"/>
-      <c r="R49" s="13" t="inlineStr"/>
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>Connections resolved</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Z-313</t>
+          <t>S-301</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Deliverable C gate pack</t>
+          <t>Structural drawing set (100%)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -4445,7 +4473,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -4471,12 +4499,12 @@
       </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Structural lead</t>
         </is>
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-S</t>
         </is>
       </c>
       <c r="Q50" s="14" t="inlineStr"/>
@@ -4485,53 +4513,53 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Z-400</t>
+          <t>M-300</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr"/>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Tender documents</t>
+          <t>Mechanical model and drawing set (100%)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>2.4 Tender</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L51" s="15" t="n"/>
@@ -4542,57 +4570,61 @@
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Lead Appointed Party</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-M</t>
         </is>
       </c>
       <c r="Q51" s="14" t="inlineStr"/>
-      <c r="R51" s="13" t="inlineStr"/>
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>BMS points identified</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Z-401</t>
+          <t>E-300</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr"/>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Tender query and addendum log</t>
+          <t>Electrical model and drawing set (100%)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>2.4 Tender</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
@@ -4602,7 +4634,7 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L52" s="15" t="n"/>
@@ -4613,12 +4645,12 @@
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>Lead Appointed Party</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-E</t>
         </is>
       </c>
       <c r="Q52" s="14" t="inlineStr"/>
@@ -4627,28 +4659,28 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Z-410</t>
+          <t>P-300</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr"/>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Conformed set</t>
+          <t>Plumbing model and drawing set (100%)</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>2.5 Conformed set</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -4658,22 +4690,22 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>PDF/DWG</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L53" s="15" t="n"/>
@@ -4684,71 +4716,67 @@
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Lead Appointed Party</t>
+          <t>MEP lead</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-P</t>
         </is>
       </c>
       <c r="Q53" s="14" t="inlineStr"/>
-      <c r="R53" s="13" t="inlineStr">
-        <is>
-          <t>Post-award addenda incorporated</t>
-        </is>
-      </c>
+      <c r="R53" s="13" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>ALL-500</t>
+          <t>FP-300</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>All disciplines</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr"/>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Construction stage models</t>
+          <t>Fire strategy and model (100%)</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L54" s="15" t="n"/>
@@ -4759,61 +4787,57 @@
       </c>
       <c r="O54" s="12" t="inlineStr">
         <is>
-          <t>Task teams</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>TIDP-ALL</t>
+          <t>TIDP-FP</t>
         </is>
       </c>
       <c r="Q54" s="14" t="inlineStr"/>
-      <c r="R54" s="13" t="inlineStr">
-        <is>
-          <t>Ongoing; revisions tracked</t>
-        </is>
-      </c>
+      <c r="R54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Z-510</t>
+          <t>LV-300</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Low Voltage</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr"/>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Request for information and submittal register</t>
+          <t>Communications and security model</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
@@ -4823,7 +4847,7 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L55" s="15" t="n"/>
@@ -4834,61 +4858,57 @@
       </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>LV lead</t>
         </is>
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-LV</t>
         </is>
       </c>
       <c r="Q55" s="14" t="inlineStr"/>
-      <c r="R55" s="13" t="inlineStr">
-        <is>
-          <t>Maintained continuously</t>
-        </is>
-      </c>
+      <c r="R55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>Z-511</t>
+          <t>Z-310</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>QS / Cost</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr"/>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Monthly status report</t>
+          <t>Bill of quantities (tender)</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
@@ -4898,7 +4918,7 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L56" s="15" t="n"/>
@@ -4909,61 +4929,57 @@
       </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Quantity Surveyor</t>
         </is>
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-Q</t>
         </is>
       </c>
       <c r="Q56" s="14" t="inlineStr"/>
-      <c r="R56" s="13" t="inlineStr">
-        <is>
-          <t>Monthly throughout construction</t>
-        </is>
-      </c>
+      <c r="R56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Z-512</t>
+          <t>Z-311</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr"/>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>As-built capture (progressive)</t>
+          <t>Specifications</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Specification</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
@@ -4973,7 +4989,7 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L57" s="15" t="n"/>
@@ -4984,61 +5000,57 @@
       </c>
       <c r="O57" s="12" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q57" s="14" t="inlineStr"/>
-      <c r="R57" s="13" t="inlineStr">
-        <is>
-          <t>Current to within one month</t>
-        </is>
-      </c>
+      <c r="R57" s="13" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>Z-513</t>
+          <t>Z-312</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr"/>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Asset data capture (tiered schedule, BEP section 14)</t>
+          <t>Specification reconciliation report</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLSX/PDF</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -5048,7 +5060,7 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L58" s="15" t="n"/>
@@ -5059,51 +5071,51 @@
       </c>
       <c r="O58" s="12" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q58" s="14" t="inlineStr"/>
       <c r="R58" s="13" t="inlineStr">
         <is>
-          <t>Tier A serialised plant, Tier B maintainable devices, Tier C warranted fabric. Required for LOD 500; reported monthly from the first month of construction</t>
+          <t>Gaps closed or formally accepted</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Z-514</t>
+          <t>FF-300</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>FF&amp;E</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr"/>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Asset data completeness report</t>
+          <t>FF&amp;E specifications and schedule</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -5113,7 +5125,7 @@
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J59" s="14" t="inlineStr">
@@ -5123,7 +5135,7 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>M12-M43</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L59" s="15" t="n"/>
@@ -5134,61 +5146,57 @@
       </c>
       <c r="O59" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Interior Designer</t>
         </is>
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-FF</t>
         </is>
       </c>
       <c r="Q59" s="14" t="inlineStr"/>
-      <c r="R59" s="13" t="inlineStr">
-        <is>
-          <t>Monthly, by tier and by volume. A tier below 95 per cent at the Deliverable D gate is a gate failure</t>
-        </is>
-      </c>
+      <c r="R59" s="13" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>M-520</t>
+          <t>Z-313</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr"/>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Commissioning point list</t>
+          <t>Deliverable C gate pack</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
@@ -5198,7 +5206,7 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>M40</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="L60" s="15" t="n"/>
@@ -5209,56 +5217,52 @@
       </c>
       <c r="O60" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Information Manager</t>
         </is>
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q60" s="14" t="inlineStr"/>
-      <c r="R60" s="13" t="inlineStr">
-        <is>
-          <t>Produced from the model for the controls contractor</t>
-        </is>
-      </c>
+      <c r="R60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>FF-600</t>
+          <t>Z-400</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>FF&amp;E</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr"/>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>FF&amp;E final schedule and procurement record</t>
+          <t>Tender documents</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>3.2 FF&amp;E</t>
+          <t>2.4 Tender</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr">
@@ -5273,7 +5277,7 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>M43</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="L61" s="15" t="n"/>
@@ -5284,71 +5288,67 @@
       </c>
       <c r="O61" s="12" t="inlineStr">
         <is>
-          <t>Interior Designer</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q61" s="14" t="inlineStr"/>
-      <c r="R61" s="13" t="inlineStr">
-        <is>
-          <t>Reconciled item by item</t>
-        </is>
-      </c>
+      <c r="R61" s="13" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>A-700</t>
+          <t>Z-401</t>
         </is>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr"/>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>As-built architectural model</t>
+          <t>Tender query and addendum log</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>2.4 Tender</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="L62" s="15" t="n"/>
@@ -5359,56 +5359,52 @@
       </c>
       <c r="O62" s="12" t="inlineStr">
         <is>
-          <t>Architecture lead</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P62" s="12" t="inlineStr">
         <is>
-          <t>TIDP-A</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q62" s="14" t="inlineStr"/>
-      <c r="R62" s="13" t="inlineStr">
-        <is>
-          <t>Verified as-built</t>
-        </is>
-      </c>
+      <c r="R62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>S-700</t>
+          <t>Z-410</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Information Management</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr"/>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>As-built structural model</t>
+          <t>Conformed set</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>2.5 Conformed set</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>PDF/DWG</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
@@ -5423,7 +5419,7 @@
       </c>
       <c r="K63" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M11</t>
         </is>
       </c>
       <c r="L63" s="15" t="n"/>
@@ -5434,32 +5430,36 @@
       </c>
       <c r="O63" s="12" t="inlineStr">
         <is>
-          <t>Structural lead</t>
+          <t>Lead Appointed Party</t>
         </is>
       </c>
       <c r="P63" s="12" t="inlineStr">
         <is>
-          <t>TIDP-S</t>
+          <t>TIDP-Z</t>
         </is>
       </c>
       <c r="Q63" s="14" t="inlineStr"/>
-      <c r="R63" s="13" t="inlineStr"/>
+      <c r="R63" s="13" t="inlineStr">
+        <is>
+          <t>Post-award addenda incorporated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>M-700</t>
+          <t>ALL-500</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>All disciplines</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr"/>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>As-built MEP model</t>
+          <t>Construction stage models</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L64" s="15" t="n"/>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="O64" s="12" t="inlineStr">
         <is>
-          <t>MEP lead</t>
+          <t>Task teams</t>
         </is>
       </c>
       <c r="P64" s="12" t="inlineStr">
         <is>
-          <t>TIDP-M</t>
+          <t>TIDP-ALL</t>
         </is>
       </c>
       <c r="Q64" s="14" t="inlineStr"/>
       <c r="R64" s="13" t="inlineStr">
         <is>
-          <t>Includes Tier A and Tier B asset data</t>
+          <t>Ongoing; revisions tracked</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Z-700</t>
+          <t>Z-510</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
@@ -5534,22 +5534,22 @@
       <c r="C65" s="12" t="inlineStr"/>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>COBie handover dataset</t>
+          <t>Request for information and submittal register</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L65" s="15" t="n"/>
@@ -5591,14 +5591,14 @@
       <c r="Q65" s="14" t="inlineStr"/>
       <c r="R65" s="13" t="inlineStr">
         <is>
-          <t>COBie 2.4</t>
+          <t>Maintained continuously</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>Z-701</t>
+          <t>Z-511</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
@@ -5609,22 +5609,22 @@
       <c r="C66" s="12" t="inlineStr"/>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Operation and maintenance / asset data pack</t>
+          <t>Monthly status report</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -5634,17 +5634,17 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L66" s="15" t="n"/>
@@ -5664,58 +5664,62 @@
         </is>
       </c>
       <c r="Q66" s="14" t="inlineStr"/>
-      <c r="R66" s="13" t="inlineStr"/>
+      <c r="R66" s="13" t="inlineStr">
+        <is>
+          <t>Monthly throughout construction</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Z-702</t>
+          <t>Z-512</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr"/>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Reconciled building management system point register</t>
+          <t>As-built capture (progressive)</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>CSV/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J67" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L67" s="15" t="n"/>
@@ -5726,71 +5730,71 @@
       </c>
       <c r="O67" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="P67" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="Q67" s="14" t="inlineStr"/>
       <c r="R67" s="13" t="inlineStr">
         <is>
-          <t>Model reconciled to the live station</t>
+          <t>Current to within one month</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>Z-703</t>
+          <t>Z-513</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Information Management</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr"/>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Deliverable D gate pack</t>
+          <t>Asset data capture (tiered schedule, BEP section 14)</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L68" s="15" t="n"/>
@@ -5801,21 +5805,25 @@
       </c>
       <c r="O68" s="12" t="inlineStr">
         <is>
-          <t>Information Manager</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="P68" s="12" t="inlineStr">
         <is>
-          <t>TIDP-Z</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="Q68" s="14" t="inlineStr"/>
-      <c r="R68" s="13" t="inlineStr"/>
+      <c r="R68" s="13" t="inlineStr">
+        <is>
+          <t>Tier A serialised plant, Tier B maintainable devices, Tier C warranted fabric. Required for LOD 500; reported monthly from the first month of construction</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Z-704</t>
+          <t>Z-514</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
@@ -5826,42 +5834,42 @@
       <c r="C69" s="12" t="inlineStr"/>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Final transmittal and project archive</t>
+          <t>Asset data completeness report</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLSX/PDF</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="J69" s="14" t="inlineStr">
         <is>
-          <t>Archived</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M12-M43</t>
         </is>
       </c>
       <c r="L69" s="15" t="n"/>
@@ -5881,11 +5889,749 @@
         </is>
       </c>
       <c r="Q69" s="14" t="inlineStr"/>
-      <c r="R69" s="13" t="inlineStr"/>
+      <c r="R69" s="13" t="inlineStr">
+        <is>
+          <t>Monthly, by tier and by volume. A tier below 95 per cent at the Deliverable D gate is a gate failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>M-520</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr"/>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Commissioning point list</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>3.1 Construction</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>M40</t>
+        </is>
+      </c>
+      <c r="L70" s="15" t="n"/>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="16">
+        <f>IF(AND(L70&lt;&gt;"",M70&lt;&gt;""),M70-L70,"")</f>
+        <v/>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>MEP lead</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-M</t>
+        </is>
+      </c>
+      <c r="Q70" s="14" t="inlineStr"/>
+      <c r="R70" s="13" t="inlineStr">
+        <is>
+          <t>Produced from the model for the controls contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>FF-600</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>FF&amp;E</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr"/>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>FF&amp;E final schedule and procurement record</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>3.2 FF&amp;E</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>M43</t>
+        </is>
+      </c>
+      <c r="L71" s="15" t="n"/>
+      <c r="M71" s="15" t="n"/>
+      <c r="N71" s="16">
+        <f>IF(AND(L71&lt;&gt;"",M71&lt;&gt;""),M71-L71,"")</f>
+        <v/>
+      </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>Interior Designer</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-FF</t>
+        </is>
+      </c>
+      <c r="Q71" s="14" t="inlineStr"/>
+      <c r="R71" s="13" t="inlineStr">
+        <is>
+          <t>Reconciled item by item</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>A-700</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr"/>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>As-built architectural model</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="n"/>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="16">
+        <f>IF(AND(L72&lt;&gt;"",M72&lt;&gt;""),M72-L72,"")</f>
+        <v/>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>Architecture lead</t>
+        </is>
+      </c>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-A</t>
+        </is>
+      </c>
+      <c r="Q72" s="14" t="inlineStr"/>
+      <c r="R72" s="13" t="inlineStr">
+        <is>
+          <t>Verified as-built</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>S-700</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr"/>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>As-built structural model</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="n"/>
+      <c r="M73" s="15" t="n"/>
+      <c r="N73" s="16">
+        <f>IF(AND(L73&lt;&gt;"",M73&lt;&gt;""),M73-L73,"")</f>
+        <v/>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>Structural lead</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-S</t>
+        </is>
+      </c>
+      <c r="Q73" s="14" t="inlineStr"/>
+      <c r="R73" s="13" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>M-700</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr"/>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>As-built MEP model</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="n"/>
+      <c r="M74" s="15" t="n"/>
+      <c r="N74" s="16">
+        <f>IF(AND(L74&lt;&gt;"",M74&lt;&gt;""),M74-L74,"")</f>
+        <v/>
+      </c>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t>MEP lead</t>
+        </is>
+      </c>
+      <c r="P74" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-M</t>
+        </is>
+      </c>
+      <c r="Q74" s="14" t="inlineStr"/>
+      <c r="R74" s="13" t="inlineStr">
+        <is>
+          <t>Includes Tier A and Tier B asset data</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Z-700</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Information Management</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr"/>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>COBie handover dataset</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L75" s="15" t="n"/>
+      <c r="M75" s="15" t="n"/>
+      <c r="N75" s="16">
+        <f>IF(AND(L75&lt;&gt;"",M75&lt;&gt;""),M75-L75,"")</f>
+        <v/>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>Information Manager</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-Z</t>
+        </is>
+      </c>
+      <c r="Q75" s="14" t="inlineStr"/>
+      <c r="R75" s="13" t="inlineStr">
+        <is>
+          <t>COBie 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Z-701</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Information Management</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr"/>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>Operation and maintenance / asset data pack</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L76" s="15" t="n"/>
+      <c r="M76" s="15" t="n"/>
+      <c r="N76" s="16">
+        <f>IF(AND(L76&lt;&gt;"",M76&lt;&gt;""),M76-L76,"")</f>
+        <v/>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>Information Manager</t>
+        </is>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-Z</t>
+        </is>
+      </c>
+      <c r="Q76" s="14" t="inlineStr"/>
+      <c r="R76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Z-702</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Information Management</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr"/>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Reconciled building management system point register</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>CSV/PDF</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="16">
+        <f>IF(AND(L77&lt;&gt;"",M77&lt;&gt;""),M77-L77,"")</f>
+        <v/>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>Information Manager</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-Z</t>
+        </is>
+      </c>
+      <c r="Q77" s="14" t="inlineStr"/>
+      <c r="R77" s="13" t="inlineStr">
+        <is>
+          <t>Model reconciled to the live station</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Z-703</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Information Management</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr"/>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Deliverable D gate pack</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L78" s="15" t="n"/>
+      <c r="M78" s="15" t="n"/>
+      <c r="N78" s="16">
+        <f>IF(AND(L78&lt;&gt;"",M78&lt;&gt;""),M78-L78,"")</f>
+        <v/>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>Information Manager</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-Z</t>
+        </is>
+      </c>
+      <c r="Q78" s="14" t="inlineStr"/>
+      <c r="R78" s="13" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Z-704</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Information Management</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr"/>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Final transmittal and project archive</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="n"/>
+      <c r="M79" s="15" t="n"/>
+      <c r="N79" s="16">
+        <f>IF(AND(L79&lt;&gt;"",M79&lt;&gt;""),M79-L79,"")</f>
+        <v/>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>Information Manager</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>TIDP-Z</t>
+        </is>
+      </c>
+      <c r="Q79" s="14" t="inlineStr"/>
+      <c r="R79" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R69"/>
-  <conditionalFormatting sqref="Q2:Q69">
+  <autoFilter ref="A1:R79"/>
+  <conditionalFormatting sqref="Q2:Q79">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Red"</formula>
     </cfRule>
@@ -5899,31 +6645,31 @@
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:R69">
+  <conditionalFormatting sqref="A2:R79">
     <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="0">
       <formula>AND($L2&lt;&gt;"",$M2="",$L2&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="B2:B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="B2:B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$A$2:$A$30</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="E2:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$C$2:$C$30</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="F2:F79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$D$2:$D$30</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="G2:G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$E$2:$E$30</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="I2:I79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="J2:J79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
+    <dataValidation sqref="Q2:Q79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Value not permitted" error="Select a value from the list. To add a permitted value, amend the Lists sheet." type="list">
       <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -7765,7 +8511,7 @@
         </is>
       </c>
       <c r="C37" s="23">
-        <f>SUMPRODUCT((MIDP!$L$2:$L$69&lt;&gt;"")*(MIDP!$M$2:$M$69="")*(MIDP!$L$2:$L$69&lt;TODAY()))</f>
+        <f>SUMPRODUCT((MIDP!$L$2:$L$79&lt;&gt;"")*(MIDP!$M$2:$M$79="")*(MIDP!$L$2:$L$79&lt;TODAY()))</f>
         <v/>
       </c>
     </row>

--- a/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_Master_Information_Delivery_Plan.xlsx
@@ -6019,7 +6019,7 @@
       </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>M43</t>
+          <t>M47</t>
         </is>
       </c>
       <c r="L71" s="15" t="n"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L72" s="15" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L73" s="15" t="n"/>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L74" s="15" t="n"/>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="K75" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L75" s="15" t="n"/>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L76" s="15" t="n"/>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L77" s="15" t="n"/>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L78" s="15" t="n"/>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>M45</t>
+          <t>M49</t>
         </is>
       </c>
       <c r="L79" s="15" t="n"/>

--- a/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_Master_Information_Delivery_Plan.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-M" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-E" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-P" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-FP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-LV" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-G" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-C" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Q" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-FF" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-C" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-I" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-W" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-ALL" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drawing schedule" sheetId="18" state="visible" r:id="rId18"/>
@@ -37,12 +37,12 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'TIDP-M'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'TIDP-E'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'TIDP-P'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'TIDP-FP'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'TIDP-LV'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'TIDP-G'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'TIDP-Y'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'TIDP-Y1'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'TIDP-C'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'TIDP-Q'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'TIDP-FF'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'TIDP-C'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'TIDP-I'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'TIDP-W'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'TIDP-ALL'!$16:$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Drawing schedule'!$B$6:$F$50</definedName>
   </definedNames>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y35"/>
+  <dimension ref="A2:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="18">
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>FP-300</t>
+          <t>LV-200</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Low Voltage</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Fire strategy and model (100%)</t>
+          <t>Low voltage containment and equipment rooms</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="N18" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P18" s="24" t="n"/>
       <c r="Q18" s="24" t="n"/>
       <c r="R18" s="21" t="n"/>
       <c r="S18" s="21" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>LV lead</t>
         </is>
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -1324,16 +1324,12 @@
         </is>
       </c>
       <c r="X18" s="22" t="inlineStr"/>
-      <c r="Y18" s="23" t="inlineStr">
-        <is>
-          <t>Transition to the design-build contractor agreed</t>
-        </is>
-      </c>
+      <c r="Y18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>FP-500</t>
+          <t>FP-300</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Construction-stage model (revisions tracked)</t>
+          <t>Fire strategy and model (100%)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -1364,46 +1360,46 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="N19" s="22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="P19" s="24" t="n"/>
       <c r="Q19" s="24" t="n"/>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="inlineStr">
         <is>
-          <t>Design-build fire contractor</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -1424,19 +1420,19 @@
       <c r="X19" s="22" t="inlineStr"/>
       <c r="Y19" s="23" t="inlineStr">
         <is>
-          <t>D-B contractor becomes engineer of record</t>
+          <t>Transition to the design-build contractor agreed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>FP-700</t>
+          <t>LV-300</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Low Voltage</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -1447,12 +1443,12 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>As-built fire protection model (LOD 500, verified)</t>
+          <t>Communications and security model and drawings</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -1462,46 +1458,46 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="N20" s="22" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="P20" s="24" t="n"/>
       <c r="Q20" s="24" t="n"/>
       <c r="R20" s="21" t="n"/>
       <c r="S20" s="21" t="inlineStr">
         <is>
-          <t>Design-build fire contractor</t>
+          <t>LV lead</t>
         </is>
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -1516,119 +1512,403 @@
       </c>
       <c r="W20" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="X20" s="22" t="inlineStr"/>
       <c r="Y20" s="23" t="inlineStr">
         <is>
+          <t>Restricted-information handling per BEP 8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>FP-500</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Fire Protection</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Construction-stage model (revisions tracked)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>3.1 Construction</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="inlineStr">
+        <is>
+          <t>Design-build fire contractor</t>
+        </is>
+      </c>
+      <c r="T21" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U21" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V21" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W21" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X21" s="22" t="inlineStr"/>
+      <c r="Y21" s="23" t="inlineStr">
+        <is>
+          <t>D-B contractor becomes engineer of record</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>LV-500</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Low Voltage</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Construction-stage model (revisions tracked)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>3.1 Construction</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="inlineStr">
+        <is>
+          <t>LV lead</t>
+        </is>
+      </c>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U22" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V22" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W22" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X22" s="22" t="inlineStr"/>
+      <c r="Y22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>FP-700</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Fire Protection</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>As-built fire protection model (LOD 500, verified)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="inlineStr">
+        <is>
+          <t>Design-build fire contractor</t>
+        </is>
+      </c>
+      <c r="T23" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr"/>
+      <c r="Y23" s="23" t="inlineStr">
+        <is>
           <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="17" t="n"/>
-      <c r="Q21" s="17" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="15" t="n"/>
-      <c r="V21" s="15" t="n"/>
-      <c r="W21" s="15" t="n"/>
-      <c r="X21" s="15" t="n"/>
-      <c r="Y21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="17" t="n"/>
-      <c r="Q22" s="17" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
-      <c r="T22" s="15" t="n"/>
-      <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="n"/>
-      <c r="W22" s="15" t="n"/>
-      <c r="X22" s="15" t="n"/>
-      <c r="Y22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
-      <c r="M23" s="15" t="n"/>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="17" t="n"/>
-      <c r="Q23" s="17" t="n"/>
-      <c r="R23" s="15" t="n"/>
-      <c r="S23" s="15" t="n"/>
-      <c r="T23" s="15" t="n"/>
-      <c r="U23" s="15" t="n"/>
-      <c r="V23" s="15" t="n"/>
-      <c r="W23" s="15" t="n"/>
-      <c r="X23" s="15" t="n"/>
-      <c r="Y23" s="15" t="n"/>
-    </row>
     <row r="24">
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="17" t="n"/>
-      <c r="Q24" s="17" t="n"/>
-      <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="n"/>
-      <c r="T24" s="15" t="n"/>
-      <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="n"/>
-      <c r="W24" s="15" t="n"/>
-      <c r="X24" s="15" t="n"/>
-      <c r="Y24" s="15" t="n"/>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>LV-700</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Low Voltage</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>As-built low voltage model (LOD 500, verified)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="inlineStr">
+        <is>
+          <t>LV lead</t>
+        </is>
+      </c>
+      <c r="T24" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X24" s="22" t="inlineStr"/>
+      <c r="Y24" s="23" t="inlineStr">
+        <is>
+          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n"/>
@@ -1916,45 +2196,149 @@
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
     </row>
+    <row r="36">
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="17" t="n"/>
+      <c r="Q36" s="17" t="n"/>
+      <c r="R36" s="15" t="n"/>
+      <c r="S36" s="15" t="n"/>
+      <c r="T36" s="15" t="n"/>
+      <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="n"/>
+      <c r="W36" s="15" t="n"/>
+      <c r="X36" s="15" t="n"/>
+      <c r="Y36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="n"/>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="17" t="n"/>
+      <c r="Q37" s="17" t="n"/>
+      <c r="R37" s="15" t="n"/>
+      <c r="S37" s="15" t="n"/>
+      <c r="T37" s="15" t="n"/>
+      <c r="U37" s="15" t="n"/>
+      <c r="V37" s="15" t="n"/>
+      <c r="W37" s="15" t="n"/>
+      <c r="X37" s="15" t="n"/>
+      <c r="Y37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="n"/>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="17" t="n"/>
+      <c r="Q38" s="17" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="15" t="n"/>
+      <c r="T38" s="15" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="n"/>
+      <c r="W38" s="15" t="n"/>
+      <c r="X38" s="15" t="n"/>
+      <c r="Y38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="15" t="n"/>
+      <c r="M39" s="15" t="n"/>
+      <c r="N39" s="15" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="17" t="n"/>
+      <c r="Q39" s="17" t="n"/>
+      <c r="R39" s="15" t="n"/>
+      <c r="S39" s="15" t="n"/>
+      <c r="T39" s="15" t="n"/>
+      <c r="U39" s="15" t="n"/>
+      <c r="V39" s="15" t="n"/>
+      <c r="W39" s="15" t="n"/>
+      <c r="X39" s="15" t="n"/>
+      <c r="Y39" s="15" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B4:H5"/>
   </mergeCells>
   <dataValidations count="12">
-    <dataValidation sqref="C17:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C17:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$30</formula1>
     </dataValidation>
-    <dataValidation sqref="E17:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E17:E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$30</formula1>
     </dataValidation>
-    <dataValidation sqref="G17:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G17:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$30</formula1>
     </dataValidation>
-    <dataValidation sqref="H17:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H17:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$J$2:$J$30</formula1>
     </dataValidation>
-    <dataValidation sqref="I17:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I17:I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$30</formula1>
     </dataValidation>
-    <dataValidation sqref="J17:J35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J17:J39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$30</formula1>
     </dataValidation>
-    <dataValidation sqref="L17:L35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L17:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="M17:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M17:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
-    <dataValidation sqref="U17:U35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U17:U39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="V17:V35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V17:V39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="W17:W35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W17:W39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="X17:X35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X17:X39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -1969,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y35"/>
+  <dimension ref="A2:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2022,7 +2406,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2620,12 @@
     <row r="17">
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>LV-200</t>
+          <t>FP-200</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>Low Voltage</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr"/>
@@ -2252,12 +2636,12 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Low voltage containment and equipment rooms</t>
+          <t>Fire strategy and suppression layout</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -2277,7 +2661,7 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -2301,12 +2685,12 @@
       <c r="R17" s="21" t="n"/>
       <c r="S17" s="21" t="inlineStr">
         <is>
-          <t>LV lead</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -2325,12 +2709,16 @@
         </is>
       </c>
       <c r="X17" s="22" t="inlineStr"/>
-      <c r="Y17" s="23" t="inlineStr"/>
+      <c r="Y17" s="23" t="inlineStr">
+        <is>
+          <t>Sprinkler and detection layout</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>LV-300</t>
+          <t>LV-200</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -2346,12 +2734,12 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Communications and security model and drawings</t>
+          <t>Low voltage containment and equipment rooms</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -2361,22 +2749,22 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>2.2 Deliverable B</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -2385,10 +2773,10 @@
         </is>
       </c>
       <c r="N18" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P18" s="24" t="n"/>
       <c r="Q18" s="24" t="n"/>
@@ -2400,7 +2788,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -2419,21 +2807,17 @@
         </is>
       </c>
       <c r="X18" s="22" t="inlineStr"/>
-      <c r="Y18" s="23" t="inlineStr">
-        <is>
-          <t>Restricted-information handling per BEP 8.1</t>
-        </is>
-      </c>
+      <c r="Y18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>LV-500</t>
+          <t>FP-300</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Low Voltage</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -2444,12 +2828,12 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Construction-stage model (revisions tracked)</t>
+          <t>Fire strategy and model (100%)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -2459,46 +2843,46 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>3.1 Construction</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="N19" s="22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="P19" s="24" t="n"/>
       <c r="Q19" s="24" t="n"/>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="inlineStr">
         <is>
-          <t>LV lead</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -2517,12 +2901,16 @@
         </is>
       </c>
       <c r="X19" s="22" t="inlineStr"/>
-      <c r="Y19" s="23" t="inlineStr"/>
+      <c r="Y19" s="23" t="inlineStr">
+        <is>
+          <t>Transition to the design-build contractor agreed</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>LV-700</t>
+          <t>LV-300</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -2538,12 +2926,12 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>As-built low voltage model (LOD 500, verified)</t>
+          <t>Communications and security model and drawings</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -2553,34 +2941,34 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>3.3 Deliverable D</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="N20" s="22" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="P20" s="24" t="n"/>
       <c r="Q20" s="24" t="n"/>
@@ -2592,7 +2980,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -2607,119 +2995,403 @@
       </c>
       <c r="W20" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="X20" s="22" t="inlineStr"/>
       <c r="Y20" s="23" t="inlineStr">
         <is>
+          <t>Restricted-information handling per BEP 8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>FP-500</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Fire Protection</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Construction-stage model (revisions tracked)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>3.1 Construction</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="inlineStr">
+        <is>
+          <t>Design-build fire contractor</t>
+        </is>
+      </c>
+      <c r="T21" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U21" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V21" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W21" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X21" s="22" t="inlineStr"/>
+      <c r="Y21" s="23" t="inlineStr">
+        <is>
+          <t>D-B contractor becomes engineer of record</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>LV-500</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Low Voltage</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Construction-stage model (revisions tracked)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>3.1 Construction</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="inlineStr">
+        <is>
+          <t>LV lead</t>
+        </is>
+      </c>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U22" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V22" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W22" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X22" s="22" t="inlineStr"/>
+      <c r="Y22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>FP-700</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Fire Protection</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>As-built fire protection model (LOD 500, verified)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="inlineStr">
+        <is>
+          <t>Design-build fire contractor</t>
+        </is>
+      </c>
+      <c r="T23" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr"/>
+      <c r="Y23" s="23" t="inlineStr">
+        <is>
           <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="17" t="n"/>
-      <c r="Q21" s="17" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="15" t="n"/>
-      <c r="V21" s="15" t="n"/>
-      <c r="W21" s="15" t="n"/>
-      <c r="X21" s="15" t="n"/>
-      <c r="Y21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="17" t="n"/>
-      <c r="Q22" s="17" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
-      <c r="T22" s="15" t="n"/>
-      <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="n"/>
-      <c r="W22" s="15" t="n"/>
-      <c r="X22" s="15" t="n"/>
-      <c r="Y22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
-      <c r="M23" s="15" t="n"/>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="17" t="n"/>
-      <c r="Q23" s="17" t="n"/>
-      <c r="R23" s="15" t="n"/>
-      <c r="S23" s="15" t="n"/>
-      <c r="T23" s="15" t="n"/>
-      <c r="U23" s="15" t="n"/>
-      <c r="V23" s="15" t="n"/>
-      <c r="W23" s="15" t="n"/>
-      <c r="X23" s="15" t="n"/>
-      <c r="Y23" s="15" t="n"/>
-    </row>
     <row r="24">
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="17" t="n"/>
-      <c r="Q24" s="17" t="n"/>
-      <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="n"/>
-      <c r="T24" s="15" t="n"/>
-      <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="n"/>
-      <c r="W24" s="15" t="n"/>
-      <c r="X24" s="15" t="n"/>
-      <c r="Y24" s="15" t="n"/>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>LV-700</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Low Voltage</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>ZZ</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>As-built low voltage model (LOD 500, verified)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>3.3 Deliverable D</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>RVT/IFC</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="inlineStr">
+        <is>
+          <t>LV lead</t>
+        </is>
+      </c>
+      <c r="T24" s="21" t="inlineStr">
+        <is>
+          <t>TIDP-Y</t>
+        </is>
+      </c>
+      <c r="U24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W24" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X24" s="22" t="inlineStr"/>
+      <c r="Y24" s="23" t="inlineStr">
+        <is>
+          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n"/>
@@ -3007,45 +3679,149 @@
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
     </row>
+    <row r="36">
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="17" t="n"/>
+      <c r="Q36" s="17" t="n"/>
+      <c r="R36" s="15" t="n"/>
+      <c r="S36" s="15" t="n"/>
+      <c r="T36" s="15" t="n"/>
+      <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="n"/>
+      <c r="W36" s="15" t="n"/>
+      <c r="X36" s="15" t="n"/>
+      <c r="Y36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="n"/>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="17" t="n"/>
+      <c r="Q37" s="17" t="n"/>
+      <c r="R37" s="15" t="n"/>
+      <c r="S37" s="15" t="n"/>
+      <c r="T37" s="15" t="n"/>
+      <c r="U37" s="15" t="n"/>
+      <c r="V37" s="15" t="n"/>
+      <c r="W37" s="15" t="n"/>
+      <c r="X37" s="15" t="n"/>
+      <c r="Y37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="n"/>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="17" t="n"/>
+      <c r="Q38" s="17" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="15" t="n"/>
+      <c r="T38" s="15" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="n"/>
+      <c r="W38" s="15" t="n"/>
+      <c r="X38" s="15" t="n"/>
+      <c r="Y38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="15" t="n"/>
+      <c r="M39" s="15" t="n"/>
+      <c r="N39" s="15" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="17" t="n"/>
+      <c r="Q39" s="17" t="n"/>
+      <c r="R39" s="15" t="n"/>
+      <c r="S39" s="15" t="n"/>
+      <c r="T39" s="15" t="n"/>
+      <c r="U39" s="15" t="n"/>
+      <c r="V39" s="15" t="n"/>
+      <c r="W39" s="15" t="n"/>
+      <c r="X39" s="15" t="n"/>
+      <c r="Y39" s="15" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B4:H5"/>
   </mergeCells>
   <dataValidations count="12">
-    <dataValidation sqref="C17:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C17:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$30</formula1>
     </dataValidation>
-    <dataValidation sqref="E17:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E17:E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$30</formula1>
     </dataValidation>
-    <dataValidation sqref="G17:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G17:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$30</formula1>
     </dataValidation>
-    <dataValidation sqref="H17:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H17:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$J$2:$J$30</formula1>
     </dataValidation>
-    <dataValidation sqref="I17:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I17:I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$30</formula1>
     </dataValidation>
-    <dataValidation sqref="J17:J35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J17:J39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$30</formula1>
     </dataValidation>
-    <dataValidation sqref="L17:L35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L17:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="M17:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M17:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
-    <dataValidation sqref="U17:U35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U17:U39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="V17:V35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V17:V39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="W17:W35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W17:W39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="X17:X35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X17:X39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -3113,7 +3889,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
     </row>
@@ -3397,7 +4173,7 @@
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -3495,7 +4271,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -3549,7 +4325,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -3593,7 +4369,7 @@
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -3687,7 +4463,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -3781,7 +4557,7 @@
       </c>
       <c r="T21" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U21" s="22" t="inlineStr">
@@ -3875,7 +4651,7 @@
       </c>
       <c r="T22" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="U22" s="22" t="inlineStr">
@@ -4636,7 +5412,7 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>BQ</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -4734,7 +5510,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>BQ</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -5295,7 +6071,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
     </row>
@@ -5535,7 +6311,7 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -5579,7 +6355,7 @@
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -5633,7 +6409,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -5677,7 +6453,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -5731,7 +6507,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -5775,7 +6551,7 @@
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -5873,7 +6649,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -6394,7 +7170,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
     </row>
@@ -6678,7 +7454,7 @@
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -6776,7 +7552,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -6830,7 +7606,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -6874,7 +7650,7 @@
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -6972,7 +7748,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -7733,7 +8509,7 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -9423,7 +10199,7 @@
     <row r="46">
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="C46" s="16">
@@ -9450,7 +10226,7 @@
     <row r="47">
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="C47" s="16">
@@ -9477,7 +10253,7 @@
     <row r="48">
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="C48" s="16">
@@ -9531,7 +10307,7 @@
     <row r="50">
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="C50" s="16">
@@ -9558,7 +10334,7 @@
     <row r="51">
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="C51" s="16">
@@ -11040,7 +11816,7 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>Type Document → Schedule; reference SC-Z-0001</t>
+          <t>Type Document → Schedule; reference SH-Z-0001</t>
         </is>
       </c>
     </row>
@@ -13370,7 +14146,7 @@
       </c>
       <c r="J2" s="15" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="K2" s="15" t="inlineStr">
@@ -13422,7 +14198,7 @@
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="K3" s="15" t="inlineStr">
@@ -13474,7 +14250,7 @@
       </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
@@ -13521,7 +14297,7 @@
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
     </row>
@@ -13558,7 +14334,7 @@
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>IE</t>
         </is>
       </c>
     </row>
@@ -13595,7 +14371,7 @@
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>M2</t>
         </is>
       </c>
     </row>
@@ -13632,7 +14408,7 @@
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
@@ -13659,7 +14435,7 @@
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -13681,7 +14457,7 @@
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>RD</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -13698,7 +14474,7 @@
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -13715,7 +14491,7 @@
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>RD</t>
         </is>
       </c>
     </row>
@@ -13727,7 +14503,7 @@
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -13739,7 +14515,7 @@
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>RP</t>
         </is>
       </c>
     </row>
@@ -13751,7 +14527,35 @@
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>BQ</t>
+          <t>SH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>VS</t>
         </is>
       </c>
     </row>
@@ -14254,7 +15058,7 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -14462,7 +15266,7 @@
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -14533,7 +15337,7 @@
       <c r="W5" s="22" t="inlineStr"/>
       <c r="X5" s="23" t="inlineStr">
         <is>
-          <t>Reference SC-Z-0002</t>
+          <t>Reference SH-Z-0002</t>
         </is>
       </c>
     </row>
@@ -14670,7 +15474,7 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -14774,7 +15578,7 @@
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -14878,7 +15682,7 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -15086,7 +15890,7 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -15157,7 +15961,7 @@
       <c r="W11" s="22" t="inlineStr"/>
       <c r="X11" s="23" t="inlineStr">
         <is>
-          <t>Reference SC-Z-0003</t>
+          <t>Reference SH-Z-0003</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15994,7 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -16438,7 +17242,7 @@
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -16746,7 +17550,7 @@
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -17312,7 +18116,7 @@
       </c>
       <c r="S32" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T32" s="22" t="inlineStr">
@@ -17470,7 +18274,7 @@
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -17986,7 +18790,7 @@
       </c>
       <c r="G39" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -18086,7 +18890,7 @@
       </c>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -18290,7 +19094,7 @@
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
@@ -18498,7 +19302,7 @@
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H44" s="21" t="inlineStr">
@@ -18702,7 +19506,7 @@
       </c>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H46" s="21" t="inlineStr">
@@ -18906,7 +19710,7 @@
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H48" s="21" t="inlineStr">
@@ -19114,7 +19918,7 @@
       </c>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H50" s="21" t="inlineStr">
@@ -19264,7 +20068,7 @@
       </c>
       <c r="S51" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T51" s="22" t="inlineStr">
@@ -19368,7 +20172,7 @@
       </c>
       <c r="S52" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T52" s="22" t="inlineStr">
@@ -19468,7 +20272,7 @@
       </c>
       <c r="S53" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T53" s="22" t="inlineStr">
@@ -19522,7 +20326,7 @@
       </c>
       <c r="G54" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H54" s="21" t="inlineStr">
@@ -19572,7 +20376,7 @@
       </c>
       <c r="S54" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T54" s="22" t="inlineStr">
@@ -19830,7 +20634,7 @@
       </c>
       <c r="G57" s="22" t="inlineStr">
         <is>
-          <t>BQ</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="H57" s="21" t="inlineStr">
@@ -19934,7 +20738,7 @@
       </c>
       <c r="G58" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H58" s="21" t="inlineStr">
@@ -19984,7 +20788,7 @@
       </c>
       <c r="S58" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="T58" s="22" t="inlineStr">
@@ -20342,7 +21146,7 @@
       </c>
       <c r="G62" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H62" s="21" t="inlineStr">
@@ -20650,7 +21454,7 @@
       </c>
       <c r="G65" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H65" s="21" t="inlineStr">
@@ -20854,7 +21658,7 @@
       </c>
       <c r="G67" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H67" s="21" t="inlineStr">
@@ -20954,7 +21758,7 @@
       </c>
       <c r="G68" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H68" s="21" t="inlineStr">
@@ -21054,7 +21858,7 @@
       </c>
       <c r="G69" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H69" s="21" t="inlineStr">
@@ -21258,7 +22062,7 @@
       </c>
       <c r="G71" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H71" s="21" t="inlineStr">
@@ -21512,7 +22316,7 @@
       </c>
       <c r="S73" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T73" s="22" t="inlineStr">
@@ -21616,7 +22420,7 @@
       </c>
       <c r="S74" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T74" s="22" t="inlineStr">
@@ -21720,7 +22524,7 @@
       </c>
       <c r="S75" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T75" s="22" t="inlineStr">
@@ -21770,7 +22574,7 @@
       </c>
       <c r="G76" s="22" t="inlineStr">
         <is>
-          <t>BQ</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="H76" s="21" t="inlineStr">
@@ -22078,7 +22882,7 @@
       </c>
       <c r="G79" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -22128,7 +22932,7 @@
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="T79" s="22" t="inlineStr">
@@ -22594,7 +23398,7 @@
       </c>
       <c r="G84" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="H84" s="21" t="inlineStr">
@@ -23356,7 +24160,7 @@
       </c>
       <c r="S91" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T91" s="22" t="inlineStr">
@@ -23460,7 +24264,7 @@
       </c>
       <c r="S92" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T92" s="22" t="inlineStr">
@@ -23560,7 +24364,7 @@
       </c>
       <c r="S93" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T93" s="22" t="inlineStr">
@@ -23660,7 +24464,7 @@
       </c>
       <c r="S94" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="T94" s="22" t="inlineStr">
@@ -23968,7 +24772,7 @@
       </c>
       <c r="S97" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="T97" s="22" t="inlineStr">
@@ -24022,7 +24826,7 @@
       </c>
       <c r="G98" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
@@ -24072,7 +24876,7 @@
       </c>
       <c r="S98" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="T98" s="22" t="inlineStr">
@@ -24330,7 +25134,7 @@
       </c>
       <c r="G101" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H101" s="21" t="inlineStr">
@@ -24638,7 +25442,7 @@
       </c>
       <c r="G104" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H104" s="21" t="inlineStr">
@@ -24742,7 +25546,7 @@
       </c>
       <c r="G105" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H105" s="21" t="inlineStr">
@@ -24792,7 +25596,7 @@
       </c>
       <c r="S105" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="T105" s="22" t="inlineStr">
@@ -24896,7 +25700,7 @@
       </c>
       <c r="S106" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FF</t>
+          <t>TIDP-I</t>
         </is>
       </c>
       <c r="T106" s="22" t="inlineStr">
@@ -25520,7 +26324,7 @@
       </c>
       <c r="S112" s="21" t="inlineStr">
         <is>
-          <t>TIDP-FP</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T112" s="22" t="inlineStr">
@@ -25624,7 +26428,7 @@
       </c>
       <c r="S113" s="21" t="inlineStr">
         <is>
-          <t>TIDP-LV</t>
+          <t>TIDP-Y</t>
         </is>
       </c>
       <c r="T113" s="22" t="inlineStr">
@@ -25728,7 +26532,7 @@
       </c>
       <c r="S114" s="21" t="inlineStr">
         <is>
-          <t>TIDP-G</t>
+          <t>TIDP-C</t>
         </is>
       </c>
       <c r="T114" s="22" t="inlineStr">
@@ -25832,7 +26636,7 @@
       </c>
       <c r="S115" s="21" t="inlineStr">
         <is>
-          <t>TIDP-C</t>
+          <t>TIDP-W</t>
         </is>
       </c>
       <c r="T115" s="22" t="inlineStr">
@@ -25886,7 +26690,7 @@
       </c>
       <c r="G116" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H116" s="21" t="inlineStr">
@@ -26094,7 +26898,7 @@
       </c>
       <c r="G118" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H118" s="21" t="inlineStr">
@@ -26302,7 +27106,7 @@
       </c>
       <c r="G120" s="22" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="H120" s="21" t="inlineStr">
@@ -26506,7 +27310,7 @@
       </c>
       <c r="G122" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
@@ -27041,7 +27845,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -27237,7 +28041,7 @@
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -27302,7 +28106,7 @@
       <c r="X20" s="22" t="inlineStr"/>
       <c r="Y20" s="23" t="inlineStr">
         <is>
-          <t>Reference SC-Z-0002</t>
+          <t>Reference SH-Z-0002</t>
         </is>
       </c>
     </row>
@@ -27433,7 +28237,7 @@
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -27531,7 +28335,7 @@
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -27727,7 +28531,7 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -27792,7 +28596,7 @@
       <c r="X25" s="22" t="inlineStr"/>
       <c r="Y25" s="23" t="inlineStr">
         <is>
-          <t>Reference SC-Z-0003</t>
+          <t>Reference SH-Z-0003</t>
         </is>
       </c>
     </row>
@@ -27825,7 +28629,7 @@
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -29001,7 +29805,7 @@
       </c>
       <c r="H38" s="22" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -29291,7 +30095,7 @@
       </c>
       <c r="H41" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -30549,7 +31353,7 @@
       </c>
       <c r="H54" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I54" s="21" t="inlineStr">
@@ -31129,7 +31933,7 @@
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I60" s="21" t="inlineStr">
@@ -31419,7 +32223,7 @@
       </c>
       <c r="H63" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
@@ -31615,7 +32419,7 @@
       </c>
       <c r="H65" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -31811,7 +32615,7 @@
       </c>
       <c r="H67" s="22" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -31909,7 +32713,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I68" s="21" t="inlineStr">
@@ -32808,7 +33612,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -33000,7 +33804,7 @@
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -33094,7 +33898,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -33286,7 +34090,7 @@
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -33482,7 +34286,7 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -34769,7 +35573,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -34961,7 +35765,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36150,7 +36954,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -36342,7 +37146,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36436,7 +37240,7 @@
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -36530,7 +37334,7 @@
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -36726,7 +37530,7 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -37825,7 +38629,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -38017,7 +38821,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -39210,7 +40014,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">

--- a/KUT_Master_Information_Delivery_Plan.xlsx
+++ b/KUT_Master_Information_Delivery_Plan.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-M" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-E" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-P" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y-FP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Y-LV" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-C" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-Q" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIDP-I" sheetId="14" state="visible" r:id="rId14"/>
@@ -37,8 +37,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'TIDP-M'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'TIDP-E'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'TIDP-P'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'TIDP-Y'!$16:$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'TIDP-Y1'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'TIDP-Y-FP'!$16:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'TIDP-Y-LV'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'TIDP-C'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'TIDP-Q'!$16:$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'TIDP-I'!$16:$16</definedName>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y39"/>
+  <dimension ref="A2:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="18">
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>LV-200</t>
+          <t>FP-300</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Low Voltage</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Low voltage containment and equipment rooms</t>
+          <t>Fire strategy and model (100%)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Document</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="N18" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P18" s="24" t="n"/>
       <c r="Q18" s="24" t="n"/>
       <c r="R18" s="21" t="n"/>
       <c r="S18" s="21" t="inlineStr">
         <is>
-          <t>LV lead</t>
+          <t>Fire lead</t>
         </is>
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -1324,12 +1324,16 @@
         </is>
       </c>
       <c r="X18" s="22" t="inlineStr"/>
-      <c r="Y18" s="23" t="inlineStr"/>
+      <c r="Y18" s="23" t="inlineStr">
+        <is>
+          <t>Transition to the design-build contractor agreed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>FP-300</t>
+          <t>FP-500</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Fire strategy and model (100%)</t>
+          <t>Construction-stage model (revisions tracked)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -1360,46 +1364,46 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>400</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N19" s="22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="P19" s="24" t="n"/>
       <c r="Q19" s="24" t="n"/>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>Design-build fire contractor</t>
         </is>
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -1420,19 +1424,19 @@
       <c r="X19" s="22" t="inlineStr"/>
       <c r="Y19" s="23" t="inlineStr">
         <is>
-          <t>Transition to the design-build contractor agreed</t>
+          <t>D-B contractor becomes engineer of record</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>LV-300</t>
+          <t>FP-700</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Low Voltage</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -1443,12 +1447,12 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Communications and security model and drawings</t>
+          <t>As-built fire protection model (LOD 500, verified)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -1458,46 +1462,46 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>3.3 Deliverable D</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N20" s="22" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="P20" s="24" t="n"/>
       <c r="Q20" s="24" t="n"/>
       <c r="R20" s="21" t="n"/>
       <c r="S20" s="21" t="inlineStr">
         <is>
-          <t>LV lead</t>
+          <t>Design-build fire contractor</t>
         </is>
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -1512,403 +1516,119 @@
       </c>
       <c r="W20" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="X20" s="22" t="inlineStr"/>
       <c r="Y20" s="23" t="inlineStr">
         <is>
-          <t>Restricted-information handling per BEP 8.1</t>
+          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>FP-500</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>Fire Protection</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>Construction-stage model (revisions tracked)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>3.1 Construction</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M21" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N21" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O21" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="inlineStr">
-        <is>
-          <t>Design-build fire contractor</t>
-        </is>
-      </c>
-      <c r="T21" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U21" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V21" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W21" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X21" s="22" t="inlineStr"/>
-      <c r="Y21" s="23" t="inlineStr">
-        <is>
-          <t>D-B contractor becomes engineer of record</t>
-        </is>
-      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="17" t="n"/>
+      <c r="Q21" s="17" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n"/>
+      <c r="W21" s="15" t="n"/>
+      <c r="X21" s="15" t="n"/>
+      <c r="Y21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>LV-500</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Low Voltage</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Construction-stage model (revisions tracked)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>3.1 Construction</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M22" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N22" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="inlineStr">
-        <is>
-          <t>LV lead</t>
-        </is>
-      </c>
-      <c r="T22" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U22" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V22" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W22" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X22" s="22" t="inlineStr"/>
-      <c r="Y22" s="23" t="inlineStr"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="17" t="n"/>
+      <c r="Q22" s="17" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n"/>
+      <c r="Y22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>FP-700</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>Fire Protection</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>As-built fire protection model (LOD 500, verified)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>3.3 Deliverable D</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N23" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="O23" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="24" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="21" t="inlineStr">
-        <is>
-          <t>Design-build fire contractor</t>
-        </is>
-      </c>
-      <c r="T23" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X23" s="22" t="inlineStr"/>
-      <c r="Y23" s="23" t="inlineStr">
-        <is>
-          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
-        </is>
-      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="17" t="n"/>
+      <c r="Q23" s="17" t="n"/>
+      <c r="R23" s="15" t="n"/>
+      <c r="S23" s="15" t="n"/>
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="15" t="n"/>
+      <c r="V23" s="15" t="n"/>
+      <c r="W23" s="15" t="n"/>
+      <c r="X23" s="15" t="n"/>
+      <c r="Y23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>LV-700</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Low Voltage</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr"/>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>As-built low voltage model (LOD 500, verified)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>3.3 Deliverable D</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N24" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="O24" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="inlineStr">
-        <is>
-          <t>LV lead</t>
-        </is>
-      </c>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X24" s="22" t="inlineStr"/>
-      <c r="Y24" s="23" t="inlineStr">
-        <is>
-          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
-        </is>
-      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="17" t="n"/>
+      <c r="Q24" s="17" t="n"/>
+      <c r="R24" s="15" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="15" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="n"/>
+      <c r="W24" s="15" t="n"/>
+      <c r="X24" s="15" t="n"/>
+      <c r="Y24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n"/>
@@ -2196,149 +1916,45 @@
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
     </row>
-    <row r="36">
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="17" t="n"/>
-      <c r="Q36" s="17" t="n"/>
-      <c r="R36" s="15" t="n"/>
-      <c r="S36" s="15" t="n"/>
-      <c r="T36" s="15" t="n"/>
-      <c r="U36" s="15" t="n"/>
-      <c r="V36" s="15" t="n"/>
-      <c r="W36" s="15" t="n"/>
-      <c r="X36" s="15" t="n"/>
-      <c r="Y36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
-      <c r="M37" s="15" t="n"/>
-      <c r="N37" s="15" t="n"/>
-      <c r="O37" s="15" t="n"/>
-      <c r="P37" s="17" t="n"/>
-      <c r="Q37" s="17" t="n"/>
-      <c r="R37" s="15" t="n"/>
-      <c r="S37" s="15" t="n"/>
-      <c r="T37" s="15" t="n"/>
-      <c r="U37" s="15" t="n"/>
-      <c r="V37" s="15" t="n"/>
-      <c r="W37" s="15" t="n"/>
-      <c r="X37" s="15" t="n"/>
-      <c r="Y37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="17" t="n"/>
-      <c r="Q38" s="17" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="15" t="n"/>
-      <c r="T38" s="15" t="n"/>
-      <c r="U38" s="15" t="n"/>
-      <c r="V38" s="15" t="n"/>
-      <c r="W38" s="15" t="n"/>
-      <c r="X38" s="15" t="n"/>
-      <c r="Y38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
-      <c r="M39" s="15" t="n"/>
-      <c r="N39" s="15" t="n"/>
-      <c r="O39" s="15" t="n"/>
-      <c r="P39" s="17" t="n"/>
-      <c r="Q39" s="17" t="n"/>
-      <c r="R39" s="15" t="n"/>
-      <c r="S39" s="15" t="n"/>
-      <c r="T39" s="15" t="n"/>
-      <c r="U39" s="15" t="n"/>
-      <c r="V39" s="15" t="n"/>
-      <c r="W39" s="15" t="n"/>
-      <c r="X39" s="15" t="n"/>
-      <c r="Y39" s="15" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B4:H5"/>
   </mergeCells>
   <dataValidations count="12">
-    <dataValidation sqref="C17:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C17:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$30</formula1>
     </dataValidation>
-    <dataValidation sqref="E17:E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E17:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$30</formula1>
     </dataValidation>
-    <dataValidation sqref="G17:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G17:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$30</formula1>
     </dataValidation>
-    <dataValidation sqref="H17:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H17:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$J$2:$J$30</formula1>
     </dataValidation>
-    <dataValidation sqref="I17:I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I17:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$30</formula1>
     </dataValidation>
-    <dataValidation sqref="J17:J39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J17:J35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$30</formula1>
     </dataValidation>
-    <dataValidation sqref="L17:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L17:L35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="M17:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M17:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
-    <dataValidation sqref="U17:U39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U17:U35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="V17:V39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V17:V35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="W17:W39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W17:W35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="X17:X39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X17:X35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -2353,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y39"/>
+  <dimension ref="A2:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2022,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2236,12 @@
     <row r="17">
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>FP-200</t>
+          <t>LV-200</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Low Voltage</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr"/>
@@ -2636,12 +2252,12 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Fire strategy and suppression layout</t>
+          <t>Low voltage containment and equipment rooms</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -2661,7 +2277,7 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -2685,12 +2301,12 @@
       <c r="R17" s="21" t="n"/>
       <c r="S17" s="21" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>LV lead</t>
         </is>
       </c>
       <c r="T17" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="U17" s="22" t="inlineStr">
@@ -2709,16 +2325,12 @@
         </is>
       </c>
       <c r="X17" s="22" t="inlineStr"/>
-      <c r="Y17" s="23" t="inlineStr">
-        <is>
-          <t>Sprinkler and detection layout</t>
-        </is>
-      </c>
+      <c r="Y17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>LV-200</t>
+          <t>LV-300</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -2734,12 +2346,12 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Low voltage containment and equipment rooms</t>
+          <t>Communications and security model and drawings</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model/Drawing</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -2749,22 +2361,22 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>2.2 Deliverable B</t>
+          <t>2.3 Deliverable C</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>RVT/IFC</t>
+          <t>RVT/PDF</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -2773,10 +2385,10 @@
         </is>
       </c>
       <c r="N18" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P18" s="24" t="n"/>
       <c r="Q18" s="24" t="n"/>
@@ -2788,7 +2400,7 @@
       </c>
       <c r="T18" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
@@ -2807,17 +2419,21 @@
         </is>
       </c>
       <c r="X18" s="22" t="inlineStr"/>
-      <c r="Y18" s="23" t="inlineStr"/>
+      <c r="Y18" s="23" t="inlineStr">
+        <is>
+          <t>Restricted-information handling per BEP 8.1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>FP-300</t>
+          <t>LV-500</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Low Voltage</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -2828,12 +2444,12 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Fire strategy and model (100%)</t>
+          <t>Construction-stage model (revisions tracked)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Model/Document</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -2843,46 +2459,46 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>3.1 Construction</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>400</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N19" s="22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="P19" s="24" t="n"/>
       <c r="Q19" s="24" t="n"/>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="inlineStr">
         <is>
-          <t>Fire lead</t>
+          <t>LV lead</t>
         </is>
       </c>
       <c r="T19" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
@@ -2901,16 +2517,12 @@
         </is>
       </c>
       <c r="X19" s="22" t="inlineStr"/>
-      <c r="Y19" s="23" t="inlineStr">
-        <is>
-          <t>Transition to the design-build contractor agreed</t>
-        </is>
-      </c>
+      <c r="Y19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>LV-300</t>
+          <t>LV-700</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -2926,12 +2538,12 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Communications and security model and drawings</t>
+          <t>As-built low voltage model (LOD 500, verified)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Model/Drawing</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -2941,34 +2553,34 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>2.3 Deliverable C</t>
+          <t>3.3 Deliverable D</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>RVT/PDF</t>
+          <t>RVT/IFC</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N20" s="22" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="P20" s="24" t="n"/>
       <c r="Q20" s="24" t="n"/>
@@ -2980,7 +2592,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="U20" s="22" t="inlineStr">
@@ -2995,403 +2607,119 @@
       </c>
       <c r="W20" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="X20" s="22" t="inlineStr"/>
       <c r="Y20" s="23" t="inlineStr">
         <is>
-          <t>Restricted-information handling per BEP 8.1</t>
+          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>FP-500</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>Fire Protection</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>Construction-stage model (revisions tracked)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>3.1 Construction</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M21" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N21" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O21" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="inlineStr">
-        <is>
-          <t>Design-build fire contractor</t>
-        </is>
-      </c>
-      <c r="T21" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U21" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V21" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W21" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X21" s="22" t="inlineStr"/>
-      <c r="Y21" s="23" t="inlineStr">
-        <is>
-          <t>D-B contractor becomes engineer of record</t>
-        </is>
-      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="17" t="n"/>
+      <c r="Q21" s="17" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n"/>
+      <c r="W21" s="15" t="n"/>
+      <c r="X21" s="15" t="n"/>
+      <c r="Y21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>LV-500</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Low Voltage</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Construction-stage model (revisions tracked)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>3.1 Construction</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M22" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N22" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="inlineStr">
-        <is>
-          <t>LV lead</t>
-        </is>
-      </c>
-      <c r="T22" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U22" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V22" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W22" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X22" s="22" t="inlineStr"/>
-      <c r="Y22" s="23" t="inlineStr"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="17" t="n"/>
+      <c r="Q22" s="17" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n"/>
+      <c r="Y22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>FP-700</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>Fire Protection</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>As-built fire protection model (LOD 500, verified)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>3.3 Deliverable D</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N23" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="O23" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="24" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="21" t="inlineStr">
-        <is>
-          <t>Design-build fire contractor</t>
-        </is>
-      </c>
-      <c r="T23" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W23" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X23" s="22" t="inlineStr"/>
-      <c r="Y23" s="23" t="inlineStr">
-        <is>
-          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
-        </is>
-      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="17" t="n"/>
+      <c r="Q23" s="17" t="n"/>
+      <c r="R23" s="15" t="n"/>
+      <c r="S23" s="15" t="n"/>
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="15" t="n"/>
+      <c r="V23" s="15" t="n"/>
+      <c r="W23" s="15" t="n"/>
+      <c r="X23" s="15" t="n"/>
+      <c r="Y23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>LV-700</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Low Voltage</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr"/>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>As-built low voltage model (LOD 500, verified)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>3.3 Deliverable D</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>RVT/IFC</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="N24" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="O24" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="inlineStr">
-        <is>
-          <t>LV lead</t>
-        </is>
-      </c>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t>TIDP-Y</t>
-        </is>
-      </c>
-      <c r="U24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W24" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X24" s="22" t="inlineStr"/>
-      <c r="Y24" s="23" t="inlineStr">
-        <is>
-          <t>Authored by the design consultant from the Contractor as-built documentation; verified by the Information Manager</t>
-        </is>
-      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="17" t="n"/>
+      <c r="Q24" s="17" t="n"/>
+      <c r="R24" s="15" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="15" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="n"/>
+      <c r="W24" s="15" t="n"/>
+      <c r="X24" s="15" t="n"/>
+      <c r="Y24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n"/>
@@ -3679,149 +3007,45 @@
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
     </row>
-    <row r="36">
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="17" t="n"/>
-      <c r="Q36" s="17" t="n"/>
-      <c r="R36" s="15" t="n"/>
-      <c r="S36" s="15" t="n"/>
-      <c r="T36" s="15" t="n"/>
-      <c r="U36" s="15" t="n"/>
-      <c r="V36" s="15" t="n"/>
-      <c r="W36" s="15" t="n"/>
-      <c r="X36" s="15" t="n"/>
-      <c r="Y36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
-      <c r="M37" s="15" t="n"/>
-      <c r="N37" s="15" t="n"/>
-      <c r="O37" s="15" t="n"/>
-      <c r="P37" s="17" t="n"/>
-      <c r="Q37" s="17" t="n"/>
-      <c r="R37" s="15" t="n"/>
-      <c r="S37" s="15" t="n"/>
-      <c r="T37" s="15" t="n"/>
-      <c r="U37" s="15" t="n"/>
-      <c r="V37" s="15" t="n"/>
-      <c r="W37" s="15" t="n"/>
-      <c r="X37" s="15" t="n"/>
-      <c r="Y37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="17" t="n"/>
-      <c r="Q38" s="17" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="15" t="n"/>
-      <c r="T38" s="15" t="n"/>
-      <c r="U38" s="15" t="n"/>
-      <c r="V38" s="15" t="n"/>
-      <c r="W38" s="15" t="n"/>
-      <c r="X38" s="15" t="n"/>
-      <c r="Y38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
-      <c r="M39" s="15" t="n"/>
-      <c r="N39" s="15" t="n"/>
-      <c r="O39" s="15" t="n"/>
-      <c r="P39" s="17" t="n"/>
-      <c r="Q39" s="17" t="n"/>
-      <c r="R39" s="15" t="n"/>
-      <c r="S39" s="15" t="n"/>
-      <c r="T39" s="15" t="n"/>
-      <c r="U39" s="15" t="n"/>
-      <c r="V39" s="15" t="n"/>
-      <c r="W39" s="15" t="n"/>
-      <c r="X39" s="15" t="n"/>
-      <c r="Y39" s="15" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B4:H5"/>
   </mergeCells>
   <dataValidations count="12">
-    <dataValidation sqref="C17:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C17:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$30</formula1>
     </dataValidation>
-    <dataValidation sqref="E17:E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E17:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$30</formula1>
     </dataValidation>
-    <dataValidation sqref="G17:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G17:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$30</formula1>
     </dataValidation>
-    <dataValidation sqref="H17:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H17:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$J$2:$J$30</formula1>
     </dataValidation>
-    <dataValidation sqref="I17:I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I17:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$30</formula1>
     </dataValidation>
-    <dataValidation sqref="J17:J39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J17:J35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$30</formula1>
     </dataValidation>
-    <dataValidation sqref="L17:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L17:L35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="M17:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M17:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
-    <dataValidation sqref="U17:U39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U17:U35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="V17:V39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V17:V35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="W17:W39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W17:W35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$30</formula1>
     </dataValidation>
-    <dataValidation sqref="X17:X39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="X17:X35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -10199,7 +9423,7 @@
     <row r="46">
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="C46" s="16">
@@ -10226,7 +9450,7 @@
     <row r="47">
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="C47" s="16">
@@ -20068,7 +19292,7 @@
       </c>
       <c r="S51" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="T51" s="22" t="inlineStr">
@@ -20172,7 +19396,7 @@
       </c>
       <c r="S52" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="T52" s="22" t="inlineStr">
@@ -22316,7 +21540,7 @@
       </c>
       <c r="S73" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="T73" s="22" t="inlineStr">
@@ -22420,7 +21644,7 @@
       </c>
       <c r="S74" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="T74" s="22" t="inlineStr">
@@ -24160,7 +23384,7 @@
       </c>
       <c r="S91" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="T91" s="22" t="inlineStr">
@@ -24264,7 +23488,7 @@
       </c>
       <c r="S92" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="T92" s="22" t="inlineStr">
@@ -26324,7 +25548,7 @@
       </c>
       <c r="S112" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-FP</t>
         </is>
       </c>
       <c r="T112" s="22" t="inlineStr">
@@ -26428,7 +25652,7 @@
       </c>
       <c r="S113" s="21" t="inlineStr">
         <is>
-          <t>TIDP-Y</t>
+          <t>TIDP-Y-LV</t>
         </is>
       </c>
       <c r="T113" s="22" t="inlineStr">
